--- a/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
@@ -639,14 +639,13 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -663,7 +662,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -673,17 +672,27 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="2" t="n"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="N4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">8450
 </t>
         </is>
       </c>
@@ -695,8 +704,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12278
-</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -707,7 +715,8 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -718,13 +727,13 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
@@ -736,13 +745,13 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -767,7 +776,7 @@
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -785,7 +794,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -809,43 +818,43 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">8235
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
@@ -857,19 +866,19 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -881,7 +890,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -893,13 +902,13 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -930,7 +939,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -942,13 +951,13 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -964,10 +973,16 @@
 </t>
         </is>
       </c>
-      <c r="L6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -984,13 +999,13 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>471</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -1013,13 +1028,13 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1031,11 +1046,16 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">578
+</t>
+        </is>
+      </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -1069,7 +1089,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1081,16 +1101,11 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">149
@@ -1099,43 +1114,44 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">54621561
+81
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11092
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">283412
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -1147,13 +1163,13 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1165,13 +1181,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1213,19 +1228,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1238,13 +1253,13 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1257,19 +1272,19 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1287,21 +1302,31 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">450
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1319,7 +1344,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11944
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -1341,16 +1366,20 @@
           <t>1458</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1361,41 +1390,45 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1717
+20 4
+89 8 6
+</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">847
+</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1412,50 +1445,50 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>134</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t xml:space="preserve">957
+</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1474,87 +1507,86 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">292
 </t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -1563,13 +1595,13 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1581,31 +1613,31 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1624,21 +1656,25 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>153</t>
@@ -1647,25 +1683,19 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1861
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1677,45 +1707,45 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>484</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -1727,19 +1757,18 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1798,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -1781,7 +1810,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1793,49 +1822,44 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1853,7 +1877,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1871,7 +1895,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1883,7 +1907,8 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1907,19 +1932,19 @@
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -1931,13 +1956,13 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1949,10 +1974,16 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -1961,64 +1992,64 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10660
-</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1174
-</t>
-        </is>
-      </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -2027,7 +2058,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2052,7 +2083,7 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2062,7 +2093,12 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">82
@@ -2077,103 +2113,102 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2134
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2462
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">745
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1268
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11182
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1393
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2198,139 +2233,137 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42292792
+64
+</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1646
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">288
 </t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4126
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110
-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2349,25 +2382,25 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1939
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2378,41 +2411,38 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">994
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2423,29 +2453,29 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2457,18 +2487,18 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t xml:space="preserve">933
+</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -2499,12 +2529,13 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2516,7 +2547,8 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">113
+61
 </t>
         </is>
       </c>
@@ -2528,8 +2560,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>007</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2544,28 +2575,32 @@
 </t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">2846
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2204
 </t>
         </is>
       </c>
@@ -2577,13 +2612,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2595,25 +2629,24 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2632,28 +2665,28 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -2664,91 +2697,94 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>436</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>004</t>
+          <t xml:space="preserve">060
+</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>30415</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t xml:space="preserve">468
+</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>691</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t xml:space="preserve">469
+</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2062
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2766,97 +2802,98 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12098
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2868,7 +2905,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -2880,19 +2917,19 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2911,7 +2948,7 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2923,37 +2960,37 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1719
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2965,19 +3002,19 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8810
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -3001,48 +3038,49 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1485
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
+          <t xml:space="preserve">24654
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3061,132 +3099,131 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>64170</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3223,126 +3260,124 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">724
+</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1880
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">2678
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">7268
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -3373,120 +3408,101 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>348</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2850
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">967
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="n"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12385
+</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="n"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -3505,7 +3521,7 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3517,25 +3533,25 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3547,7 +3563,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3559,21 +3575,17 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">31
@@ -3582,24 +3594,25 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3611,31 +3624,31 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -3660,8 +3673,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3671,13 +3683,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3694,7 +3705,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3705,68 +3716,56 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>6054</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">835
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>6054</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -3791,84 +3790,73 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1309
+</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1681
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">288
 </t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3041</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -3877,7 +3865,8 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3894,13 +3883,13 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">144944
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -3912,13 +3901,13 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3937,77 +3926,87 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1026
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1102
-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>4654</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11946
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4028,7 +4027,7 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4046,7 +4045,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4077,19 +4076,19 @@
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4101,19 +4100,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1608
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4125,22 +4124,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
@@ -4150,7 +4144,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4162,49 +4156,49 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2956
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4229,13 +4223,13 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4253,7 +4247,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4265,24 +4259,24 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -4318,7 +4312,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -4330,7 +4324,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12296
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
@@ -4342,13 +4336,13 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4373,25 +4367,20 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
+          <t xml:space="preserve">13532
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4401,7 +4390,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4412,7 +4401,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4424,28 +4413,19 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
+          <t xml:space="preserve">1391
 </t>
         </is>
       </c>
@@ -4457,40 +4437,39 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
-</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2980
-</t>
-        </is>
-      </c>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="n"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr"/>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>964</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>346</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4508,7 +4487,7 @@
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4520,7 +4499,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4532,13 +4511,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8106
-</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -4548,10 +4526,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4562,55 +4545,50 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">856
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
@@ -4622,19 +4600,19 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4653,7 +4631,7 @@
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -4677,74 +4655,75 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>4824</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1924
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4756,7 +4735,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4774,7 +4753,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4805,13 +4784,13 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4823,25 +4802,25 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4859,25 +4838,25 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -4889,44 +4868,39 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="n"/>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">196
 </t>
         </is>
       </c>
+      <c r="X33" s="2" t="n"/>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -4945,7 +4919,7 @@
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -4957,13 +4931,13 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4975,7 +4949,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -4987,7 +4961,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4999,19 +4973,19 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -5023,7 +4997,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5035,13 +5009,13 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">576
 </t>
         </is>
       </c>
@@ -5059,7 +5033,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5071,13 +5045,13 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5096,7 +5070,7 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5108,7 +5082,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5120,19 +5094,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -5144,7 +5118,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5157,7 +5131,7 @@
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">9006
 </t>
         </is>
       </c>
@@ -5169,13 +5143,13 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -5187,43 +5161,43 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -5242,7 +5216,7 @@
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">486
 </t>
         </is>
       </c>
@@ -5254,13 +5228,13 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5272,49 +5246,48 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>001</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1756
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1726
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5326,13 +5299,13 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5344,11 +5317,16 @@
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -5363,13 +5341,13 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
@@ -5388,7 +5366,7 @@
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
@@ -5398,16 +5376,10 @@
 </t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
+      <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5418,13 +5390,13 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -5435,77 +5407,76 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t xml:space="preserve">999
+</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11395
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
+          <t xml:space="preserve">1348
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">19228
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="n"/>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3868
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
@@ -5530,59 +5501,60 @@
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">3921
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18950
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">7
+9
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>273</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5594,7 +5566,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">7378
 </t>
         </is>
       </c>
@@ -5606,53 +5578,59 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">77
+248
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">117
+203
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>00578</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">62
@@ -5680,25 +5658,25 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5714,98 +5692,89 @@
 </t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122084
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2394
+          <t xml:space="preserve">1354
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5836,26 +5805,25 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -5866,48 +5834,43 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11262
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="n"/>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2616
 </t>
         </is>
       </c>
@@ -5919,43 +5882,33 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="n"/>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="n"/>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5974,32 +5927,32 @@
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6011,7 +5964,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -6023,80 +5976,80 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">8401
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="n"/>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">765
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">765
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6115,55 +6068,55 @@
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1708
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -6175,28 +6128,23 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="n"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">210
@@ -6211,36 +6159,46 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="n"/>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="n"/>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6262,18 +6220,18 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -6284,25 +6242,20 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4150
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -6314,7 +6267,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6326,31 +6279,31 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -6360,12 +6313,7 @@
 </t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
+      <c r="V43" s="2" t="n"/>
       <c r="W43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -6374,13 +6322,13 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14270
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6400,18 +6348,23 @@
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -6420,80 +6373,98 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">11256
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">626
+</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470
+</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1164
-</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="n"/>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1470
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="n"/>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="n"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">148
@@ -6516,32 +6487,42 @@
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -6553,68 +6534,80 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">9984
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n"/>
+          <t>0526</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01111
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
-</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1439
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3179
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="n"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="n"/>
-      <c r="X45" s="2" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -6634,25 +6627,21 @@
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">89
+6
+</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6677,7 +6666,7 @@
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6689,74 +6678,61 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">831
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">2919292795
+24
+12
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">655
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="n"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6772,43 +6748,44 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">751717747
+60
+1
+17
+</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">610111197
+422
 </t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+7
+</t>
+        </is>
+      </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
@@ -624,43 +624,88 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 </t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P4" s="2" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1 39
+</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -670,7 +715,12 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="2" t="n"/>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
       <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n"/>
@@ -691,40 +741,100 @@
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11289
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -742,7 +852,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -777,17 +887,26 @@
         </is>
       </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -797,52 +916,87 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">6564
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -882,25 +1036,46 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -910,21 +1085,50 @@
 </t>
         </is>
       </c>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11186
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
-      <c r="R7" s="2" t="n"/>
-      <c r="S7" s="2" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
@@ -934,7 +1138,12 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="2" t="n"/>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">196
@@ -943,18 +1152,19 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -973,40 +1183,65 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n"/>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="inlineStr">
         <is>
@@ -1014,40 +1249,50 @@
 </t>
         </is>
       </c>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">450
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n"/>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2258
+</t>
+        </is>
+      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="n"/>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="n"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1061,51 +1306,141 @@
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1428
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1152
+</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">571
+</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">346
+</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">423
+</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1428
+</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1060
+</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
+          <t xml:space="preserve">20991
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="n"/>
-      <c r="W9" s="2" t="n"/>
+          <t xml:space="preserve">9926
+</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2299
+</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">6150
 </t>
         </is>
       </c>
@@ -1121,112 +1456,141 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t xml:space="preserve">113
+</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">847
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19438
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10960
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11026
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t xml:space="preserve">510
+</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2294610</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -1242,73 +1606,109 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1284
+</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">1184
+</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n"/>
+          <t xml:space="preserve">8909
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
       <c r="U11" s="2" t="n"/>
       <c r="V11" s="2" t="n"/>
       <c r="W11" s="2" t="n"/>
@@ -1327,47 +1727,142 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n"/>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">513
+</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1971
+</t>
+        </is>
+      </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1383,98 +1878,142 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 1
+</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n"/>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n"/>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11820
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n"/>
+          <t xml:space="preserve">2835
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1200
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29412
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="n"/>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="n"/>
-      <c r="Y13" s="2" t="n"/>
-      <c r="Z13" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -1487,77 +2026,136 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2331
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11916
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2868
+</t>
+        </is>
+      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="n"/>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1574,89 +2172,124 @@
         </is>
       </c>
       <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="n"/>
-      <c r="X15" s="2" t="n"/>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1610
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="n"/>
+      <c r="Z15" s="2" t="n"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -1669,72 +2302,136 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+          <t xml:space="preserve">11988
+</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0909
+</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11139
+</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11910
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9006
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9808
+</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22812
+</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="n"/>
-      <c r="U16" s="2" t="n"/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2662
+</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="n"/>
+          <t xml:space="preserve">1528
+</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
+</t>
+        </is>
+      </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">3048
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1750,124 +2447,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11288
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0098
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
+          <t xml:space="preserve">1001
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9106
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11282
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
-</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="n"/>
+          <t xml:space="preserve">522
+</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2993
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1883,90 +2598,135 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 1
+</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1804
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1136
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1621
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1146
+</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="n"/>
-      <c r="S18" s="2" t="n"/>
-      <c r="T18" s="2" t="n"/>
-      <c r="U18" s="2" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="n"/>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1604
-</t>
-        </is>
-      </c>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+      <c r="Y18" s="2" t="n"/>
+      <c r="Z18" s="2" t="n"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>11</t>
@@ -1979,77 +2739,131 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
+          <t xml:space="preserve">17 6
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29481
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="n"/>
-      <c r="V19" s="2" t="n"/>
+          <t xml:space="preserve">468
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="n"/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">340
+</t>
+        </is>
+      </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11495
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2065,52 +2879,137 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
-      <c r="S20" s="2" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11174
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="n"/>
-      <c r="V20" s="2" t="n"/>
-      <c r="W20" s="2" t="n"/>
-      <c r="X20" s="2" t="n"/>
-      <c r="Y20" s="2" t="n"/>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2126,55 +3025,135 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126
-</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9485
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="n"/>
-      <c r="W21" s="2" t="n"/>
-      <c r="X21" s="2" t="n"/>
-      <c r="Y21" s="2" t="n"/>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -2187,61 +3166,137 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
-      <c r="Q22" s="2" t="n"/>
-      <c r="R22" s="2" t="n"/>
-      <c r="S22" s="2" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="n"/>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -2257,26 +3312,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1956
+</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n"/>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -2286,53 +3366,92 @@
 </t>
         </is>
       </c>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="n"/>
+          <t xml:space="preserve">9268
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="n"/>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11804
+</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="n"/>
+          <t xml:space="preserve">2679
+</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="X23" s="2" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
+</t>
+        </is>
+      </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">22161
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2348,128 +3467,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19456
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t xml:space="preserve">281
+</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11034
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10804
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12678
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11235
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2206
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2485,99 +3618,129 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 1 5
+</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
+          <t xml:space="preserve">1028
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1569
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">12218
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="n"/>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="n"/>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1864
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="n"/>
       <c r="Y25" s="2" t="n"/>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
+      <c r="Z25" s="2" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -2590,70 +3753,149 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="n"/>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="n"/>
-      <c r="Y26" s="2" t="n"/>
-      <c r="Z26" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">385
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -2666,51 +3908,97 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n"/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="n"/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1889
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -2719,19 +4007,34 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="n"/>
-      <c r="W27" s="2" t="n"/>
-      <c r="X27" s="2" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="Y27" s="2" t="n"/>
       <c r="Z27" s="2" t="n"/>
       <c r="AA27" t="inlineStr">
@@ -2747,52 +4050,127 @@
         </is>
       </c>
       <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="n"/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52940
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n"/>
-      <c r="T28" s="2" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2207
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">567
+</t>
+        </is>
+      </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="n"/>
-      <c r="W28" s="2" t="n"/>
-      <c r="X28" s="2" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y28" s="2" t="n"/>
       <c r="Z28" s="2" t="n"/>
       <c r="AA28" t="inlineStr">
@@ -2807,50 +4185,145 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n"/>
-      <c r="T29" s="2" t="n"/>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6595
+</t>
+        </is>
+      </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="n"/>
-      <c r="W29" s="2" t="n"/>
-      <c r="X29" s="2" t="n"/>
-      <c r="Y29" s="2" t="n"/>
-      <c r="Z29" s="2" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -2863,87 +4336,142 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19524
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18168
+</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1310
+</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n"/>
+          <t xml:space="preserve">20161
+</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26814
+</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">914
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">8365
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n"/>
+          <t xml:space="preserve">4200
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1320
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">10820
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="n"/>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2989
+</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18182
+</t>
+        </is>
+      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="n"/>
-      <c r="Y30" s="2" t="n"/>
+          <t xml:space="preserve">9856
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3162
+</t>
+        </is>
+      </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
@@ -2959,98 +4487,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13098
-</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28100
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">23183
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
+</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="n"/>
-      <c r="T31" s="2" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="n"/>
-      <c r="Y31" s="2" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
+      </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3066,90 +4638,145 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n"/>
+          <t xml:space="preserve">2189
+</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="n"/>
-      <c r="R32" s="2" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">568
+</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="n"/>
-      <c r="X32" s="2" t="n"/>
-      <c r="Y32" s="2" t="n"/>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -3162,109 +4789,141 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t xml:space="preserve">286
+</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">4200
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">750
 </t>
         </is>
       </c>
@@ -3281,58 +4940,133 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="2" t="n"/>
-      <c r="U34" s="2" t="n"/>
-      <c r="V34" s="2" t="n"/>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00216
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12846
+</t>
+        </is>
+      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="n"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="Y34" s="2" t="n"/>
       <c r="Z34" s="2" t="n"/>
       <c r="AA34" t="inlineStr">
@@ -3347,60 +5081,135 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n"/>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11908
+</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="n"/>
-      <c r="R35" s="2" t="n"/>
-      <c r="S35" s="2" t="n"/>
-      <c r="T35" s="2" t="n"/>
-      <c r="U35" s="2" t="n"/>
-      <c r="V35" s="2" t="n"/>
-      <c r="W35" s="2" t="n"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622
+</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -3418,44 +5227,138 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="n"/>
-      <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="n"/>
-      <c r="T36" s="2" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="n"/>
-      <c r="W36" s="2" t="n"/>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
       <c r="Z36" s="2" t="n"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -3469,60 +5372,145 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11208
+</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">802
+</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8080
+</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218164
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2198
+</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
+          <t xml:space="preserve">905
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0116
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10822
+</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="n"/>
-      <c r="Q37" s="2" t="n"/>
-      <c r="R37" s="2" t="n"/>
-      <c r="S37" s="2" t="n"/>
+          <t xml:space="preserve">49208
+</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11022
+</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="n"/>
-      <c r="W37" s="2" t="n"/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1098
+</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Y37" s="2" t="n"/>
-      <c r="Z37" s="2" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1068
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2312
+</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3535,101 +5523,140 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11308
-</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2486
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t xml:space="preserve">1165
+</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8924208
-</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">861
+</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="n"/>
-      <c r="T38" s="2" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">387
+</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71481
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="n"/>
-      <c r="X38" s="2" t="n"/>
-      <c r="Y38" s="2" t="n"/>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39312
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="n"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3642,94 +5669,141 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n"/>
+          <t xml:space="preserve">1026
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9421
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8986
+</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="n"/>
+          <t xml:space="preserve">408
+</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
+      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">577
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X39" s="2" t="n"/>
-      <c r="Y39" s="2" t="n"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
+      </c>
       <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
@@ -3743,51 +5817,121 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3164
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="n"/>
-      <c r="R40" s="2" t="n"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -3796,13 +5940,13 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -3819,59 +5963,138 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8401
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="n"/>
-      <c r="Q41" s="2" t="n"/>
-      <c r="R41" s="2" t="n"/>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">623
+</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="n"/>
+          <t xml:space="preserve">11084
+</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="n"/>
+          <t xml:space="preserve">765
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -3884,44 +6107,130 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11916
-</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>85401</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="n"/>
-      <c r="Q42" s="2" t="n"/>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="S42" s="2" t="n"/>
-      <c r="T42" s="2" t="n"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
       <c r="U42" s="2" t="n"/>
-      <c r="V42" s="2" t="n"/>
-      <c r="W42" s="2" t="n"/>
-      <c r="X42" s="2" t="n"/>
-      <c r="Y42" s="2" t="n"/>
-      <c r="Z42" s="2" t="n"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -3934,55 +6243,144 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n"/>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8094
+</t>
+        </is>
+      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="2" t="n"/>
-      <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="n"/>
-      <c r="W43" s="2" t="n"/>
-      <c r="X43" s="2" t="n"/>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1299
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="Z43" s="2" t="n"/>
       <c r="AA43" t="inlineStr">
         <is>
           <t>30</t>
@@ -3995,61 +6393,77 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">8181
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11120
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n"/>
+          <t xml:space="preserve">1800
+</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n"/>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="n"/>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -4065,17 +6479,42 @@
 </t>
         </is>
       </c>
-      <c r="S44" s="2" t="n"/>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">470
 </t>
         </is>
       </c>
-      <c r="U44" s="2" t="n"/>
-      <c r="V44" s="2" t="n"/>
-      <c r="W44" s="2" t="n"/>
-      <c r="X44" s="2" t="n"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">148
@@ -4095,13 +6534,33 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0221
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2884
+</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
@@ -4113,7 +6572,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -4125,13 +6584,13 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">11896
 </t>
         </is>
       </c>
@@ -4141,8 +6600,18 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11027
+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179926
+</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -4151,15 +6620,25 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16560
-</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="n"/>
-      <c r="S45" s="2" t="n"/>
+          <t xml:space="preserve">16620
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">2179
 </t>
         </is>
       </c>
@@ -4169,12 +6648,27 @@
 </t>
         </is>
       </c>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="n"/>
-      <c r="X45" s="2" t="n"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3228
+</t>
+        </is>
+      </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">644
 </t>
         </is>
       </c>
@@ -4191,17 +6685,22 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n"/>
+          <t xml:space="preserve">2719
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4213,13 +6712,13 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4236,8 +6735,18 @@
 </t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1854
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">831
@@ -4250,22 +6759,42 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="2" t="n"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -4274,13 +6803,13 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
@@ -624,12 +624,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">278
@@ -656,7 +651,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -678,10 +673,15 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -699,13 +699,13 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1 39
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -717,7 +717,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -791,13 +791,13 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -834,7 +834,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -852,7 +852,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -864,7 +864,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -889,7 +889,7 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -936,7 +936,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -960,7 +960,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -984,7 +984,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
@@ -1036,7 +1036,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -1049,12 +1049,7 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -1075,7 +1070,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1087,13 +1082,14 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">074
+</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1108,7 +1104,12 @@
 </t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -1123,12 +1124,13 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -1140,8 +1142,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1152,19 +1153,19 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1183,13 +1184,13 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1201,13 +1202,13 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1219,7 +1220,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1263,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">450
+          <t xml:space="preserve">459
 </t>
         </is>
       </c>
@@ -1275,7 +1276,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1318,15 +1319,10 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1152
-</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -1338,13 +1334,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">864
 </t>
         </is>
       </c>
@@ -1362,19 +1357,19 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">423
+          <t xml:space="preserve">4235
 </t>
         </is>
       </c>
@@ -1386,49 +1381,49 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1860
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20991
+          <t xml:space="preserve">2631
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1440,7 +1435,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6150
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
@@ -1459,87 +1454,88 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2292
+</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">847
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">292
 </t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1134
-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -1554,7 +1550,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1584,7 +1580,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
@@ -1609,14 +1605,12 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1627,8 +1621,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1639,8 +1632,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1663,7 +1655,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -1675,7 +1667,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8909
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1687,7 +1679,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1705,7 +1697,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">475
 </t>
         </is>
       </c>
@@ -1727,15 +1719,10 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513
-</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1795,7 +1782,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1813,25 +1800,20 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
-</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="n"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -1850,7 +1832,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -1862,7 +1844,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1878,21 +1860,16 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 1
-</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -1910,7 +1887,8 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1927,7 +1905,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1939,7 +1917,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -1951,13 +1929,14 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2835
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1969,24 +1948,20 @@
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t xml:space="preserve">571
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -2004,16 +1979,10 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t>7640</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -2026,7 +1995,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">274
@@ -2041,16 +2010,11 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2331
-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -2060,7 +2024,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -2084,7 +2048,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -2102,7 +2066,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2868
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2114,7 +2078,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2126,7 +2090,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -2138,7 +2102,8 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>034</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2149,7 +2114,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2186,7 +2151,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2838
 </t>
         </is>
       </c>
@@ -2217,7 +2182,7 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2235,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2305,16 +2270,11 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11988
-</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0909
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10388
+</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">11139
@@ -2329,22 +2289,21 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">906
 </t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9006
-</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -2353,8 +2312,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2363,33 +2321,28 @@
 </t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22812
+          <t xml:space="preserve">8382
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1021
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -2407,31 +2360,30 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1528
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>933</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3048
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -2447,15 +2399,10 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2479,7 +2426,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2504,7 +2451,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2516,13 +2463,13 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2534,7 +2481,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2552,7 +2499,7 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2564,19 +2511,18 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">604
 </t>
         </is>
       </c>
@@ -2598,39 +2544,27 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 1
-</t>
-        </is>
-      </c>
+      <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804
-</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -2642,25 +2576,24 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -2672,31 +2605,31 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">788
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">5298
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2714,8 +2647,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2739,7 +2671,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">296
@@ -2761,7 +2698,7 @@
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 6
+          <t xml:space="preserve">17 5
 </t>
         </is>
       </c>
@@ -2779,7 +2716,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -2791,7 +2728,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2803,14 +2740,13 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>701</t>
         </is>
       </c>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2828,18 +2764,19 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -2857,13 +2794,13 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2882,7 +2819,7 @@
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2907,7 +2844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -2919,7 +2856,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -2931,7 +2868,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2979,8 +2916,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -3003,7 +2939,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -3025,10 +2961,10 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3040,7 +2976,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3064,19 +3000,19 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3088,7 +3024,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3119,13 +3055,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2560
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3143,13 +3079,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -3169,19 +3104,19 @@
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -3259,7 +3194,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3277,7 +3212,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -3290,7 +3225,7 @@
       <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3312,15 +3247,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -3332,31 +3262,30 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">5295
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3368,7 +3297,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -3380,49 +3309,48 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9268
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11804
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2679
+          <t xml:space="preserve">82678
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>976</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3433,25 +3361,24 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22161
-</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3467,12 +3394,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">291
@@ -3487,19 +3409,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2375
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -3515,7 +3437,12 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -3572,7 +3499,7 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3590,7 +3517,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3618,26 +3545,22 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8 1 5
-</t>
-        </is>
-      </c>
+      <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3649,13 +3572,13 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3667,46 +3590,41 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1569
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -3715,8 +3633,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3728,13 +3645,13 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3755,7 +3672,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3767,37 +3684,37 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -3819,14 +3736,10 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -3862,13 +3775,12 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>438</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">2494
 </t>
         </is>
       </c>
@@ -3886,14 +3798,13 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3908,27 +3819,22 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 0
-</t>
-        </is>
-      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -3940,7 +3846,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -3952,13 +3858,13 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3976,13 +3882,13 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1889
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -3992,7 +3898,11 @@
 </t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4007,7 +3917,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -4049,20 +3959,25 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">94
@@ -4101,31 +4016,31 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52940
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4137,7 +4052,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -4185,10 +4100,10 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4278,20 +4193,19 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6595
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -4308,7 +4222,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -4336,46 +4250,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19524
+          <t xml:space="preserve">13348
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18168
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20161
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26814
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -4393,25 +4312,23 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8365
+          <t xml:space="preserve">1854
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200
-</t>
+          <t>434644</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4423,7 +4340,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10820
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
@@ -4441,38 +4358,35 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>704</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18182
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162
+          <t xml:space="preserve">31362
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4489,7 +4403,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4525,7 +4439,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4535,10 +4449,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85 2
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -4616,8 +4535,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
-</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4638,33 +4556,23 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4712,68 +4620,65 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>714</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1946
+</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z32" s="2" t="n"/>
@@ -4789,21 +4694,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4827,13 +4727,13 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4851,13 +4751,13 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4869,19 +4769,18 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -4911,7 +4810,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -4940,10 +4839,10 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4955,13 +4854,13 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -5009,7 +4908,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -5021,13 +4920,13 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5051,7 +4950,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -5063,7 +4962,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -5083,7 +4982,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5101,7 +5000,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5119,7 +5018,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5155,25 +5054,25 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11908
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5203,7 +5102,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5230,19 +5129,19 @@
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5260,7 +5159,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5284,7 +5183,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">072
 </t>
         </is>
       </c>
@@ -5332,7 +5231,8 @@
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -5375,13 +5275,13 @@
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11208
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">8 82
 </t>
         </is>
       </c>
@@ -5393,62 +5293,60 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">4986
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8080
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218164
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0116
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49208
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5459,26 +5357,25 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11022
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">2086
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>447</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -5489,7 +5386,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5501,13 +5398,13 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1068
+          <t xml:space="preserve">1560
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -5562,13 +5459,13 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5580,7 +5477,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -5616,13 +5513,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">387
+          <t xml:space="preserve">577
 </t>
         </is>
       </c>
@@ -5634,8 +5530,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5669,126 +5564,116 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8986
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5800,7 +5685,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -5817,10 +5702,10 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5832,19 +5717,19 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3164
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5854,15 +5739,10 @@
 </t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
@@ -5892,19 +5772,19 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5916,7 +5796,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
@@ -5965,13 +5845,13 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -5989,7 +5869,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6001,8 +5881,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -6013,7 +5892,8 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">58
+</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -6024,13 +5904,13 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6053,16 +5933,21 @@
 </t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11084
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -6080,7 +5965,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -6122,8 +6007,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -6132,19 +6016,19 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">64
 </t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
-      </c>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6165,7 +6049,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6189,8 +6073,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr"/>
@@ -6209,13 +6092,13 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6227,7 +6110,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6243,24 +6126,20 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1185
@@ -6269,13 +6148,13 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6323,7 +6202,7 @@
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8094
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -6335,31 +6214,30 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -6393,22 +6271,27 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8181
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
@@ -6426,29 +6309,33 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -6463,7 +6350,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6491,12 +6378,7 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1236
-</t>
-        </is>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -6505,8 +6387,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
@@ -6534,40 +6415,34 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2884
+          <t xml:space="preserve">8306
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -6578,19 +6453,19 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
+          <t xml:space="preserve">10896
 </t>
         </is>
       </c>
@@ -6602,16 +6477,11 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11027
-</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179926
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -6620,20 +6490,17 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16620
-</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -6650,19 +6517,19 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">1 8
 </t>
         </is>
       </c>
@@ -6688,8 +6555,7 @@
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2719
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6700,7 +6566,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6712,13 +6578,13 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6737,13 +6603,13 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -6761,7 +6627,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -6773,7 +6639,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -6785,7 +6651,7 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6809,7 +6675,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">16 54
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
@@ -627,34 +627,34 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9230
+</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">68
@@ -675,53 +675,58 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1868
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n"/>
       <c r="W4" s="2" t="n"/>
@@ -740,7 +745,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -785,77 +795,82 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">836
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548
+</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -864,7 +879,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">565
 </t>
         </is>
       </c>
@@ -886,10 +901,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -901,7 +921,8 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -954,7 +975,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -984,7 +1005,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -996,7 +1017,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1036,7 +1057,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -1049,7 +1075,12 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -1070,7 +1101,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -1082,13 +1113,13 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">074
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -1100,7 +1131,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1112,7 +1143,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">3004
 </t>
         </is>
       </c>
@@ -1130,19 +1161,20 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">6564
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">258
+</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1153,7 +1185,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
@@ -1165,7 +1197,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1184,31 +1216,37 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">92359
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1224,10 +1262,15 @@
 </t>
         </is>
       </c>
-      <c r="L8" s="2" t="n"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1243,7 +1286,12 @@
 </t>
         </is>
       </c>
-      <c r="P8" s="2" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">306
@@ -1264,36 +1312,46 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">420
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="n"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1309,104 +1367,109 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1488
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8871
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">348
+</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">364
+</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">832
+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4235
+</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1428
 </t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
-</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">917
-</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">098
-</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4235
-</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">11960
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1826
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2631
+          <t xml:space="preserve">92551
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1417,25 +1480,25 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">9714
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2299
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -1454,7 +1517,7 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1472,7 +1535,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1490,13 +1553,13 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1544,13 +1607,13 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1580,13 +1643,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">5 9
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1605,12 +1668,13 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">1284
+</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1621,18 +1685,18 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>414</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1667,7 +1731,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -1679,7 +1743,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -1691,21 +1755,41 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="n"/>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="2" t="n"/>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">489
+</t>
+        </is>
+      </c>
       <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1719,10 +1803,15 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1734,7 +1823,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">431
 </t>
         </is>
       </c>
@@ -1776,7 +1865,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -1794,7 +1883,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1810,41 +1899,43 @@
 </t>
         </is>
       </c>
-      <c r="S12" s="2" t="n"/>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2571
+</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="n"/>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1860,43 +1951,43 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">60
 </t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
@@ -1905,7 +1996,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1929,13 +2020,13 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1945,20 +2036,30 @@
 </t>
         </is>
       </c>
-      <c r="R13" s="2" t="n"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256
@@ -1967,7 +2068,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1979,10 +2080,16 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -1995,7 +2102,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">274
@@ -2014,8 +2121,18 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">66
@@ -2024,7 +2141,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -2048,13 +2165,13 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -2072,31 +2189,31 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">515
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2114,7 +2231,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -2151,7 +2268,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2838
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2179,10 +2296,15 @@
 </t>
         </is>
       </c>
-      <c r="K15" s="2" t="n"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -2200,11 +2322,16 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">288
@@ -2231,7 +2358,7 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2243,7 +2370,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2253,8 +2380,18 @@
 </t>
         </is>
       </c>
-      <c r="Y15" s="2" t="n"/>
-      <c r="Z15" s="2" t="n"/>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">660
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -2267,17 +2404,27 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10388
-</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1388
+</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11139
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2289,19 +2436,18 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t xml:space="preserve">2882
+</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2312,7 +2458,8 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">920
+</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2321,16 +2468,26 @@
 </t>
         </is>
       </c>
-      <c r="N16" s="2" t="n"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9094
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8382
+          <t xml:space="preserve">1382
 </t>
         </is>
       </c>
@@ -2348,8 +2505,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2372,7 +2528,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>953</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2383,7 +2539,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2402,7 +2558,7 @@
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -2420,13 +2576,13 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2442,7 +2598,7 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -2457,7 +2613,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -2469,31 +2625,31 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
@@ -2511,24 +2667,25 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
+          <t xml:space="preserve">10685
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">810 8
 </t>
         </is>
       </c>
@@ -2547,48 +2704,48 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>884</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>136</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>496</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2599,14 +2756,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">788
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,14 +2772,12 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2635,30 +2788,42 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="n"/>
-      <c r="Y18" s="2" t="n"/>
-      <c r="Z18" s="2" t="n"/>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">007
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">380
+</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2671,12 +2836,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">296
@@ -2691,14 +2851,19 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n"/>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2716,7 +2881,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2734,19 +2899,25 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
@@ -2764,7 +2935,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -2794,13 +2965,13 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2940
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2816,7 +2987,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">106
@@ -2835,16 +3011,21 @@
 </t>
         </is>
       </c>
-      <c r="G20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2856,7 +3037,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -2910,13 +3091,14 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">475
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2939,13 +3121,13 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -2961,10 +3143,10 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -3000,19 +3182,18 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3024,7 +3205,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -3040,7 +3221,12 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -3055,13 +3241,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -3073,22 +3259,28 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="n"/>
+          <t xml:space="preserve">390
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3101,7 +3293,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -3110,13 +3307,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -3152,7 +3349,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3164,7 +3361,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3188,13 +3385,13 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -3212,17 +3409,21 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>4454</t>
+        </is>
+      </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">160
@@ -3231,7 +3432,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">2549
 </t>
         </is>
       </c>
@@ -3247,10 +3448,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3262,30 +3468,30 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t xml:space="preserve">848
+</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295
-</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -3297,42 +3503,43 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">1404
+</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
@@ -3344,41 +3551,40 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82678
-</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t xml:space="preserve">919
+</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">11235
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">9356
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>70501</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">6528
 </t>
         </is>
       </c>
@@ -3394,7 +3600,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">291
@@ -3409,7 +3615,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2375
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3421,49 +3627,44 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">054
 </t>
         </is>
       </c>
@@ -3475,7 +3676,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">2841
 </t>
         </is>
       </c>
@@ -3493,43 +3694,43 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3545,34 +3746,34 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">19 4
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3596,35 +3797,36 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">076
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr"/>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -3633,13 +3835,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr"/>
@@ -3651,13 +3852,26 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="n"/>
-      <c r="Y25" s="2" t="n"/>
-      <c r="Z25" s="2" t="n"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3670,39 +3884,34 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -3714,7 +3923,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -3736,16 +3945,21 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="2" t="n"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -3769,18 +3983,19 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">522
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3798,13 +4013,14 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">1128
+</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3822,19 +4038,19 @@
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3846,49 +4062,49 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -3900,7 +4116,8 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -3917,19 +4134,19 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
@@ -3945,8 +4162,18 @@
 </t>
         </is>
       </c>
-      <c r="Y27" s="2" t="n"/>
-      <c r="Z27" s="2" t="n"/>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -3959,22 +4186,27 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3986,7 +4218,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
@@ -3998,13 +4230,13 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4016,19 +4248,19 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -4058,7 +4290,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
@@ -4070,24 +4302,34 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="n"/>
-      <c r="Z28" s="2" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">599
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4100,67 +4342,72 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -4193,19 +4440,20 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -4222,7 +4470,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -4250,15 +4498,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13348
+          <t xml:space="preserve">1332
 </t>
         </is>
       </c>
@@ -4270,60 +4513,57 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">095
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">484
-</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">2800
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
-</t>
+          <t>94348</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>434644</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4358,35 +4598,35 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>716</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31362
+          <t xml:space="preserve">9162
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>476</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4403,7 +4643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4427,13 +4667,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4449,15 +4689,10 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85 2
-</t>
-        </is>
-      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4469,13 +4704,13 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">2051
 </t>
         </is>
       </c>
@@ -4493,16 +4728,16 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">598
@@ -4511,7 +4746,7 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4535,12 +4770,13 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4559,11 +4795,15 @@
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -4578,8 +4818,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4590,13 +4829,13 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4612,76 +4851,64 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">048
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t xml:space="preserve">968
+</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">44 128
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="n"/>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -4694,22 +4921,22 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4733,7 +4960,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4751,13 +4978,13 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -4775,7 +5002,8 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -4786,19 +5014,19 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">2560
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4810,7 +5038,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -4826,7 +5054,12 @@
 </t>
         </is>
       </c>
-      <c r="Z33" s="2" t="n"/>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>22</t>
@@ -4839,115 +5072,115 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">482
+</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">246
@@ -4966,8 +5199,18 @@
 </t>
         </is>
       </c>
-      <c r="Y34" s="2" t="n"/>
-      <c r="Z34" s="2" t="n"/>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">670
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -4980,33 +5223,28 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -5036,13 +5274,13 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5054,25 +5292,25 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5084,7 +5322,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5102,7 +5340,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">10188
 </t>
         </is>
       </c>
@@ -5112,8 +5350,18 @@
 </t>
         </is>
       </c>
-      <c r="Y35" s="2" t="n"/>
-      <c r="Z35" s="2" t="n"/>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5129,19 +5377,19 @@
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5177,13 +5425,13 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">072
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -5213,7 +5461,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -5225,13 +5473,13 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5255,7 +5503,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
@@ -5275,49 +5523,48 @@
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 82
+          <t xml:space="preserve">88218
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4986
+          <t xml:space="preserve">456
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109
-</t>
+          <t>409</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1172
+</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5328,54 +5575,53 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">1494
+</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">1318
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">10822
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -5386,19 +5632,19 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">9981
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1560
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -5420,7 +5666,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -5441,7 +5687,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5459,16 +5705,11 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -5477,13 +5718,13 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5513,12 +5754,13 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">577
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5530,28 +5772,34 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">12790 1
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">11119
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5564,16 +5812,21 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5584,36 +5837,30 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -5625,50 +5872,51 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">848
+</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr"/>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5685,11 +5933,15 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="2" t="n"/>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5702,89 +5954,94 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1080
-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5796,13 +6053,13 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1944
 </t>
         </is>
       </c>
@@ -5845,32 +6102,31 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5881,7 +6137,8 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5904,13 +6161,13 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5920,7 +6177,12 @@
 </t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">226
@@ -5929,7 +6191,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5941,19 +6203,19 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5965,21 +6227,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">765
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -5995,7 +6253,7 @@
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1486
 </t>
         </is>
       </c>
@@ -6007,28 +6265,34 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2201
+</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1940
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">654
+</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6037,19 +6301,19 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6073,17 +6337,28 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">520
 </t>
         </is>
       </c>
-      <c r="U42" s="2" t="n"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -6104,13 +6379,13 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6126,44 +6401,49 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1501
+</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11744
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1185
-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6172,90 +6452,91 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0250
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">570
-</t>
-        </is>
-      </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -6273,51 +6554,52 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">2120
 </t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6338,31 +6620,31 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">1548
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -6378,7 +6660,12 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -6387,7 +6674,8 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
@@ -6402,7 +6690,12 @@
 </t>
         </is>
       </c>
-      <c r="Z44" s="2" t="n"/>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6418,54 +6711,55 @@
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11658
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8306
+          <t xml:space="preserve">1359
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t xml:space="preserve">922
+</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">594
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10896
+          <t xml:space="preserve">1096
 </t>
         </is>
       </c>
@@ -6477,11 +6771,16 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4990
+</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -6490,56 +6789,64 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">11911
+</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179
+          <t xml:space="preserve">5179
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">15430
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
+          <t xml:space="preserve">3929
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="n"/>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111411
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6552,10 +6859,11 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6566,13 +6874,13 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -6594,7 +6902,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="n"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72162 8
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">183
@@ -6609,77 +6922,82 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">5549
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">530
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">831
 </t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="Y46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">36
 </t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16 54
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="n"/>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
@@ -627,104 +627,87 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="U4" s="2" t="n"/>
@@ -747,146 +730,122 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>565</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -903,146 +862,122 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>583</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1059,146 +994,122 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1216,140 +1127,117 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92359
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,104 +1255,87 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871
-</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
-</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11960
-</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92551
-</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1474,32 +1345,27 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9714
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,140 +1383,117 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
+          <t>847</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 9
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,8 +1511,7 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1679,8 +1521,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1695,62 +1536,52 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1765,8 +1596,7 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1786,8 +1616,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>589</t>
         </is>
       </c>
       <c r="Z11" s="2" t="n"/>
@@ -1805,116 +1634,97 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2571
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V12" s="2" t="n"/>
@@ -1935,8 +1745,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1954,140 +1763,117 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2105,140 +1891,117 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">515
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2256,140 +2019,117 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2406,38 +2146,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2882
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2452,26 +2186,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9094
-</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2481,26 +2211,22 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382
-</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2510,20 +2236,17 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2533,14 +2256,12 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>020</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2558,135 +2279,113 @@
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10685
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810 8
-</t>
+          <t>254 1</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2704,8 +2403,7 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2750,8 +2448,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2766,8 +2463,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2782,8 +2478,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2808,20 +2503,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">007
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2839,140 +2531,117 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2940
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2989,146 +2658,122 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
+          <t>475</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3146,38 +2791,32 @@
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3187,98 +2826,82 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3295,128 +2918,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3426,14 +3028,12 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3450,38 +3050,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3491,62 +3085,52 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>529</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3556,20 +3140,17 @@
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11235
-</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9356
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
@@ -3584,8 +3165,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6528
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3603,135 +3183,113 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">054
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3748,63 +3306,53 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 4
-</t>
+          <t>19 2</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">076
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3829,8 +3377,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3846,8 +3393,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3862,14 +3408,12 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3887,140 +3431,117 @@
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4035,143 +3556,124 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4188,146 +3690,122 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4344,146 +3822,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4501,20 +3955,17 @@
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
-</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">095
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4524,8 +3975,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4535,8 +3985,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4551,14 +4000,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4568,38 +4015,32 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
-</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2989
-</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -4609,8 +4050,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
@@ -4620,8 +4060,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9162
-</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4643,141 +4082,118 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2051
-</t>
+          <t>051</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4795,8 +4211,7 @@
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4806,14 +4221,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -4823,39 +4236,33 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
@@ -4871,14 +4278,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4894,14 +4299,12 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44 128
-</t>
+          <t>91 22</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4924,140 +4327,117 @@
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5075,140 +4455,117 @@
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5226,140 +4583,117 @@
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5377,134 +4711,112 @@
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z36" s="2" t="n"/>
@@ -5520,29 +4832,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88218
-</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5557,20 +4869,17 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -5585,38 +4894,32 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
-</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
-</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
-</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -5626,32 +4929,27 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
-</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5669,135 +4967,113 @@
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12790 1
-</t>
+          <t>11 1</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11119
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5814,8 +5090,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5825,14 +5100,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5848,38 +5121,32 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5899,14 +5166,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -5921,20 +5186,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>645</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5957,134 +5219,112 @@
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="Z40" s="2" t="n"/>
@@ -6102,26 +5342,22 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -6131,110 +5367,92 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>765</t>
         </is>
       </c>
       <c r="Z41" s="2" t="n"/>
@@ -6253,140 +5471,117 @@
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1486
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6404,140 +5599,117 @@
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11744
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6554,146 +5726,122 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1548
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6708,143 +5856,124 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11658
-</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
-</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">594
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
-</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11911
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15430
-</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
-</t>
+          <t>935</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111411
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6862,140 +5991,117 @@
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72162 8
-</t>
+          <t>5 18</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5549
-</t>
+          <t>51 1</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>081 1</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>842</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>254 1</t>
+          <t>90 21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>001</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>220</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>256</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>142</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
@@ -4299,12 +4299,12 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>91 22</t>
+          <t>91 191</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -4580,7 +4580,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>242</t>
@@ -4608,7 +4612,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4834,7 +4838,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4909,12 +4913,12 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4934,12 +4938,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>950</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -5023,7 +5027,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5058,12 +5062,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11 1</t>
+          <t>011 1</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -5073,7 +5077,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5342,7 +5346,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5372,7 +5376,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5427,7 +5431,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5437,7 +5441,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5452,7 +5456,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z41" s="2" t="n"/>
@@ -5481,7 +5485,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5511,7 +5515,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -5609,7 +5613,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5664,7 +5668,7 @@
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -5674,12 +5678,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5726,12 +5730,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5741,7 +5745,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5751,12 +5755,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5786,7 +5790,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5796,7 +5800,7 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -5858,7 +5862,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5893,7 +5897,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -5913,12 +5917,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5938,12 +5942,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5963,7 +5967,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -6026,7 +6030,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>5 18</t>
+          <t>28 08</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6041,7 +6045,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>51 1</t>
+          <t>2011 0</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -6051,7 +6055,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6101,7 +6105,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/904/Top_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>583</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>318</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>081 1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>892</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>107</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>90 21</t>
+          <t>08 8</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>00</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>595</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>572</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>208</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
@@ -4299,12 +4299,12 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>91 191</t>
+          <t>00 10</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -4580,11 +4580,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>242</t>
@@ -4848,7 +4844,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4918,7 +4914,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4943,7 +4939,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>014</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -5027,7 +5023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5047,32 +5043,32 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>05 0</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
           <t>01</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>011 1</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5233,7 +5229,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5308,7 +5304,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -5346,7 +5342,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5376,7 +5372,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5431,7 +5427,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>628</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5456,7 +5452,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>765</t>
         </is>
       </c>
       <c r="Z41" s="2" t="n"/>
@@ -5698,7 +5694,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>290</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -5730,7 +5726,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5755,7 +5751,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5790,7 +5786,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5845,7 +5841,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5862,7 +5858,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5897,7 +5893,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>615</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -5917,7 +5913,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5962,7 +5958,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
@@ -6030,7 +6026,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>28 08</t>
+          <t>2 08</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6045,7 +6041,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2011 0</t>
+          <t>200 0</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -6055,7 +6051,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
